--- a/ms_tables/tableS1_disparity_n_large_fam.xlsx
+++ b/ms_tables/tableS1_disparity_n_large_fam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/GitHub/GvsP/ms_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BD6461-365B-9143-B85B-46E64F0CD147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EF0479-4925-FF4F-B3A9-AB4AF66E5BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27320" yWindow="620" windowWidth="27320" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -831,19 +831,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>970279</xdr:colOff>
+      <xdr:colOff>970278</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3297</xdr:rowOff>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="6" name="TextBox 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80FF1561-8169-A04A-B955-24F6AAF5F7E5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DC9DFF2-949F-B347-BF10-F1CF3B3E5591}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -851,7 +851,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4516119" y="206497"/>
+              <a:off x="4516118" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -917,7 +917,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -975,7 +975,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -989,13 +989,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="6" name="TextBox 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80FF1561-8169-A04A-B955-24F6AAF5F7E5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DC9DFF2-949F-B347-BF10-F1CF3B3E5591}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1003,7 +1003,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4516119" y="206497"/>
+              <a:off x="4516118" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1042,37 +1042,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1085,19 +1085,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>782321</xdr:colOff>
+      <xdr:colOff>782320</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1337</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="7" name="TextBox 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8381AF5-215A-E440-A7A1-18A16DC97603}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA1C71A9-871B-F841-87BA-A30C91B951B4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1105,7 +1105,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2428241" y="204537"/>
+              <a:off x="2428240" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1140,6 +1140,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1171,73 +1229,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="7" name="TextBox 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8381AF5-215A-E440-A7A1-18A16DC97603}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA1C71A9-871B-F841-87BA-A30C91B951B4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1245,7 +1251,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2428241" y="204537"/>
+              <a:off x="2428240" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1275,9 +1281,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -1286,25 +1322,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1315,19 +1333,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1003249</xdr:colOff>
+      <xdr:colOff>1003248</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3920</xdr:rowOff>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="8" name="TextBox 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0374FE45-DC0A-5441-BB0C-2690A1E52D44}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB9C4ECE-2F7B-5B4C-9A16-D18CAACC8D56}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1335,7 +1353,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3472129" y="207120"/>
+              <a:off x="3472128" y="205783"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1467,13 +1485,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="8" name="TextBox 7">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0374FE45-DC0A-5441-BB0C-2690A1E52D44}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB9C4ECE-2F7B-5B4C-9A16-D18CAACC8D56}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1481,7 +1499,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3472129" y="207120"/>
+              <a:off x="3472128" y="205783"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1563,19 +1581,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>949959</xdr:colOff>
+      <xdr:colOff>980438</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3297</xdr:rowOff>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="TextBox 11">
+            <xdr:cNvPr id="9" name="TextBox 8">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E859D357-3850-0145-AEB1-7EE90BD9EA16}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F588BBAE-65FD-D940-9643-C16E1DD7FDDA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1583,7 +1601,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8082279" y="206497"/>
+              <a:off x="8112758" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1649,7 +1667,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1707,7 +1725,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1721,13 +1739,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="12" name="TextBox 11">
+            <xdr:cNvPr id="9" name="TextBox 8">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E859D357-3850-0145-AEB1-7EE90BD9EA16}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F588BBAE-65FD-D940-9643-C16E1DD7FDDA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1735,7 +1753,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8082279" y="206497"/>
+              <a:off x="8112758" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1774,37 +1792,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1817,19 +1835,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1371601</xdr:colOff>
+      <xdr:colOff>1402080</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1337</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="13" name="TextBox 12">
+            <xdr:cNvPr id="10" name="TextBox 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F30AAD2-2E6D-7E4F-A1C9-8F6C31245646}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71CBCB09-520B-CF4C-BAE4-2C3260388D1E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1837,7 +1855,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5994401" y="204537"/>
+              <a:off x="6024880" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1872,6 +1890,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1903,73 +1979,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="13" name="TextBox 12">
+            <xdr:cNvPr id="10" name="TextBox 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F30AAD2-2E6D-7E4F-A1C9-8F6C31245646}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71CBCB09-520B-CF4C-BAE4-2C3260388D1E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1977,7 +2001,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5994401" y="204537"/>
+              <a:off x="6024880" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2007,9 +2031,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2018,25 +2072,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2047,19 +2083,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>982929</xdr:colOff>
+      <xdr:colOff>1013408</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3920</xdr:rowOff>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="14" name="TextBox 13">
+            <xdr:cNvPr id="11" name="TextBox 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F192DFE-06BE-9949-A031-AAD0ECF420D7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD34E11A-9870-1B4B-8E70-E7A6E2E23C2A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2067,7 +2103,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7038289" y="207120"/>
+              <a:off x="7068768" y="205783"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2199,13 +2235,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="14" name="TextBox 13">
+            <xdr:cNvPr id="11" name="TextBox 10">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F192DFE-06BE-9949-A031-AAD0ECF420D7}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD34E11A-9870-1B4B-8E70-E7A6E2E23C2A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2213,7 +2249,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7038289" y="207120"/>
+              <a:off x="7068768" y="205783"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2295,19 +2331,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>949959</xdr:colOff>
+      <xdr:colOff>980438</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3297</xdr:rowOff>
+      <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="TextBox 14">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B4458D-0864-B04E-8B30-9110C35FA11D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0455E0AF-280B-C744-A17F-9D1C9B0D3C9B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2315,7 +2351,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11638279" y="206497"/>
+              <a:off x="11668758" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2381,7 +2417,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2439,7 +2475,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2453,13 +2489,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="15" name="TextBox 14">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B4458D-0864-B04E-8B30-9110C35FA11D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0455E0AF-280B-C744-A17F-9D1C9B0D3C9B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2467,7 +2503,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11638279" y="206497"/>
+              <a:off x="11668758" y="205160"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2506,37 +2542,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -2549,19 +2585,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1351281</xdr:colOff>
+      <xdr:colOff>1381760</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1337</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="TextBox 15">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72803C8E-7FA8-584B-AAD3-92C507E2631F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D131A2-EA8F-964E-87BB-F93AEE942C0F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2569,7 +2605,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9550401" y="204537"/>
+              <a:off x="9580880" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2604,6 +2640,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2635,73 +2729,21 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="TextBox 15">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72803C8E-7FA8-584B-AAD3-92C507E2631F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10D131A2-EA8F-964E-87BB-F93AEE942C0F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2709,7 +2751,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9550401" y="204537"/>
+              <a:off x="9580880" y="203200"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2739,9 +2781,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2750,25 +2822,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2779,19 +2833,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>982929</xdr:colOff>
+      <xdr:colOff>1013408</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3920</xdr:rowOff>
+      <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="707834" cy="181231"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="17" name="TextBox 16">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36DCFE64-1586-5343-8F21-22BDF3E07957}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3600F5A2-C7AC-EA4C-B43A-1838CC08B7EB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2799,7 +2853,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10594289" y="207120"/>
+              <a:off x="10624768" y="205783"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2931,13 +2985,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="17" name="TextBox 16">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36DCFE64-1586-5343-8F21-22BDF3E07957}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3600F5A2-C7AC-EA4C-B43A-1838CC08B7EB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2945,7 +2999,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10594289" y="207120"/>
+              <a:off x="10624768" y="205783"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
